--- a/src_excel/Mineraux.xlsx
+++ b/src_excel/Mineraux.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28122"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\FaLabo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manah\Documents\nutrition\src_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3753E131-D0F1-42EF-83E9-795E5829ED2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{7CA45FF0-0BE6-4D07-8D12-F04F88A90154}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5772"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,20 +24,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t xml:space="preserve">PARAMETRES </t>
   </si>
   <si>
-    <t xml:space="preserve">UNITE </t>
-  </si>
-  <si>
     <t>Potassium</t>
   </si>
   <si>
-    <t>g/100g</t>
-  </si>
-  <si>
     <t>Magnésium</t>
   </si>
   <si>
@@ -60,22 +53,31 @@
     <t>Essai2_K067_Lentille_verte</t>
   </si>
   <si>
+    <t>Essai1_K068_Lentille_corail</t>
+  </si>
+  <si>
+    <t>Essai2_K068_Lentille_corail</t>
+  </si>
+  <si>
+    <t>Essai1_K069_Lentille_noire</t>
+  </si>
+  <si>
+    <t>Essai2_K069_Lentille_noire</t>
+  </si>
+  <si>
+    <t>Essai3_K067_Lentille_verte</t>
+  </si>
+  <si>
+    <t>Essai3_K068_Lentille_corail</t>
+  </si>
+  <si>
+    <t>Essai3_K069_Lentille_noire</t>
+  </si>
+  <si>
     <t>Moyenne_K067_Lentille_verte</t>
   </si>
   <si>
-    <t>Essai1_K068_Lentille_corail</t>
-  </si>
-  <si>
-    <t>Essai2_K068_Lentille_corail</t>
-  </si>
-  <si>
     <t>Moyenne_K068_Lentille_corail</t>
-  </si>
-  <si>
-    <t>Essai1_K069_Lentille_noire</t>
-  </si>
-  <si>
-    <t>Essai2_K069_Lentille_noire</t>
   </si>
   <si>
     <t>Moyenne_K069_Lentille_noire</t>
@@ -84,7 +86,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
@@ -154,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
@@ -170,6 +172,12 @@
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -484,61 +492,67 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EEE09D4-248A-4F7F-AE8F-32AFB444527D}">
-  <dimension ref="A1:K7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="47.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
+      <c r="B2" s="4">
+        <v>0.99046076699999996</v>
       </c>
       <c r="C2" s="4">
-        <v>0.99046076699999996</v>
-      </c>
-      <c r="D2" s="4">
         <v>0.97562428000000001</v>
       </c>
-      <c r="E2" s="5">
-        <f t="shared" ref="E2:E7" si="0">AVERAGE(C2:D2)</f>
-        <v>0.98304252349999999</v>
+      <c r="D2" s="2">
+        <v>0.98299999999999998</v>
+      </c>
+      <c r="E2" s="7">
+        <f>AVERAGE(B2:D2)</f>
+        <v>0.98302834900000002</v>
       </c>
       <c r="F2" s="4">
         <v>1.019125525</v>
@@ -546,37 +560,43 @@
       <c r="G2" s="4">
         <v>0.837572188</v>
       </c>
-      <c r="H2" s="5">
-        <f t="shared" ref="H2:H7" si="1">AVERAGE(F2:G2)</f>
-        <v>0.92834885649999999</v>
-      </c>
-      <c r="I2" s="4">
+      <c r="H2" s="4">
+        <v>0.92830000000000001</v>
+      </c>
+      <c r="I2" s="7">
+        <f>AVERAGE(F2:H2)</f>
+        <v>0.928332571</v>
+      </c>
+      <c r="J2" s="4">
         <v>1.065050289</v>
       </c>
-      <c r="J2" s="4">
+      <c r="K2" s="4">
         <v>1.009660094</v>
       </c>
-      <c r="K2" s="5">
-        <f t="shared" ref="K2:K7" si="2">AVERAGE(I2:J2)</f>
-        <v>1.0373551915000001</v>
+      <c r="L2" s="6">
+        <v>1.0374000000000001</v>
+      </c>
+      <c r="M2" s="5">
+        <f>AVERAGE(J2:L2)</f>
+        <v>1.0373701276666667</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="B3" s="4">
+        <v>0.105168566</v>
       </c>
       <c r="C3" s="4">
-        <v>0.105168566</v>
-      </c>
-      <c r="D3" s="4">
         <v>0.104708404</v>
       </c>
-      <c r="E3" s="5">
-        <f t="shared" si="0"/>
-        <v>0.104938485</v>
+      <c r="D3" s="2">
+        <v>0.10489999999999999</v>
+      </c>
+      <c r="E3" s="7">
+        <f t="shared" ref="E3:E7" si="0">AVERAGE(B3:D3)</f>
+        <v>0.10492565666666666</v>
       </c>
       <c r="F3" s="4">
         <v>6.5266578000000006E-2</v>
@@ -584,37 +604,43 @@
       <c r="G3" s="4">
         <v>5.3543427999999997E-2</v>
       </c>
-      <c r="H3" s="5">
-        <f t="shared" si="1"/>
-        <v>5.9405002999999998E-2</v>
-      </c>
-      <c r="I3" s="4">
+      <c r="H3" s="4">
+        <v>5.9400000000000001E-2</v>
+      </c>
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I7" si="1">AVERAGE(F3:H3)</f>
+        <v>5.9403335333333335E-2</v>
+      </c>
+      <c r="J3" s="4">
         <v>5.4495391999999997E-2</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>2.8942323999999998E-2</v>
       </c>
-      <c r="K3" s="5">
-        <f t="shared" si="2"/>
-        <v>4.1718857999999998E-2</v>
+      <c r="L3" s="6">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="M3" s="5">
+        <f t="shared" ref="M3:M7" si="2">AVERAGE(J3:L3)</f>
+        <v>4.1712572000000003E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="B4" s="4">
+        <v>5.2337408000000002E-2</v>
+      </c>
       <c r="C4" s="4">
-        <v>5.2337408000000002E-2</v>
-      </c>
-      <c r="D4" s="4">
         <v>5.5291992999999998E-2</v>
       </c>
-      <c r="E4" s="5">
+      <c r="D4" s="2">
+        <v>5.3800000000000001E-2</v>
+      </c>
+      <c r="E4" s="7">
         <f t="shared" si="0"/>
-        <v>5.38147005E-2</v>
+        <v>5.3809800333333331E-2</v>
       </c>
       <c r="F4" s="4">
         <v>7.2924519999999996E-3</v>
@@ -622,37 +648,43 @@
       <c r="G4" s="4">
         <v>7.1117150000000002E-3</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
+        <v>7.1999999999999998E-3</v>
+      </c>
+      <c r="I4" s="7">
         <f t="shared" si="1"/>
-        <v>7.2020834999999995E-3</v>
-      </c>
-      <c r="I4" s="4">
+        <v>7.2013889999999999E-3</v>
+      </c>
+      <c r="J4" s="4">
         <v>9.5797160000000003E-3</v>
       </c>
-      <c r="J4" s="4">
+      <c r="K4" s="4">
         <v>1.007952E-2</v>
       </c>
-      <c r="K4" s="5">
+      <c r="L4" s="6">
+        <v>9.7999999999999997E-3</v>
+      </c>
+      <c r="M4" s="5">
         <f t="shared" si="2"/>
-        <v>9.829618E-3</v>
+        <v>9.8197453333333327E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="B5" s="4">
+        <v>4.8742910000000002E-3</v>
       </c>
       <c r="C5" s="4">
-        <v>4.8742910000000002E-3</v>
-      </c>
-      <c r="D5" s="4">
         <v>5.0260030000000002E-3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="D5" s="2">
+        <v>5.0000000000000001E-3</v>
+      </c>
+      <c r="E5" s="7">
         <f t="shared" si="0"/>
-        <v>4.9501470000000002E-3</v>
+        <v>4.9667646666666674E-3</v>
       </c>
       <c r="F5" s="4">
         <v>3.5969140000000001E-3</v>
@@ -660,37 +692,43 @@
       <c r="G5" s="4">
         <v>3.6409530000000002E-3</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
+        <v>3.5999999999999999E-3</v>
+      </c>
+      <c r="I5" s="7">
         <f t="shared" si="1"/>
-        <v>3.6189335000000001E-3</v>
-      </c>
-      <c r="I5" s="4">
+        <v>3.6126223333333338E-3</v>
+      </c>
+      <c r="J5" s="4">
         <v>3.3653289999999998E-3</v>
       </c>
-      <c r="J5" s="4">
+      <c r="K5" s="4">
         <v>3.429428E-3</v>
       </c>
-      <c r="K5" s="5">
+      <c r="L5" s="6">
+        <v>3.3999999999999998E-3</v>
+      </c>
+      <c r="M5" s="5">
         <f t="shared" si="2"/>
-        <v>3.3973785000000001E-3</v>
+        <v>3.3982523333333336E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="B6" s="4">
+        <v>7.1791123999999998E-2</v>
       </c>
       <c r="C6" s="4">
-        <v>7.1791123999999998E-2</v>
-      </c>
-      <c r="D6" s="4">
         <v>7.2015562000000005E-2</v>
       </c>
-      <c r="E6" s="5">
+      <c r="D6" s="2">
+        <v>7.1900000000000006E-2</v>
+      </c>
+      <c r="E6" s="7">
         <f t="shared" si="0"/>
-        <v>7.1903343000000008E-2</v>
+        <v>7.1902228666666679E-2</v>
       </c>
       <c r="F6" s="4">
         <v>0.15079963599999999</v>
@@ -698,37 +736,43 @@
       <c r="G6" s="4">
         <v>0.14896546399999999</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="4">
+        <v>0.14990000000000001</v>
+      </c>
+      <c r="I6" s="7">
         <f t="shared" si="1"/>
-        <v>0.14988255</v>
-      </c>
-      <c r="I6" s="4">
+        <v>0.14988836666666669</v>
+      </c>
+      <c r="J6" s="4">
         <v>9.3158437999999996E-2</v>
       </c>
-      <c r="J6" s="4">
+      <c r="K6" s="4">
         <v>9.1647530000000005E-2</v>
       </c>
-      <c r="K6" s="5">
+      <c r="L6" s="6">
+        <v>9.2399999999999996E-2</v>
+      </c>
+      <c r="M6" s="5">
         <f t="shared" si="2"/>
-        <v>9.2402983999999994E-2</v>
+        <v>9.2401989333333323E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>3</v>
+        <v>6</v>
+      </c>
+      <c r="B7" s="4">
+        <v>0.36850749500000002</v>
       </c>
       <c r="C7" s="4">
-        <v>0.36850749500000002</v>
-      </c>
-      <c r="D7" s="4">
         <v>0.37420302500000002</v>
       </c>
-      <c r="E7" s="5">
+      <c r="D7" s="2">
+        <v>0.37140000000000001</v>
+      </c>
+      <c r="E7" s="7">
         <f t="shared" si="0"/>
-        <v>0.37135526000000002</v>
+        <v>0.37137017333333339</v>
       </c>
       <c r="F7" s="4">
         <v>0.27313492299999997</v>
@@ -736,22 +780,29 @@
       <c r="G7" s="4">
         <v>0.38447699499999999</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7" s="4">
+        <v>0.32879999999999998</v>
+      </c>
+      <c r="I7" s="7">
         <f t="shared" si="1"/>
-        <v>0.32880595899999998</v>
-      </c>
-      <c r="I7" s="4">
+        <v>0.32880397266666667</v>
+      </c>
+      <c r="J7" s="4">
         <v>0.26914681200000001</v>
       </c>
-      <c r="J7" s="4">
+      <c r="K7" s="4">
         <v>0.33855041699999999</v>
       </c>
-      <c r="K7" s="5">
+      <c r="L7" s="6">
+        <v>0.30380000000000001</v>
+      </c>
+      <c r="M7" s="5">
         <f t="shared" si="2"/>
-        <v>0.3038486145</v>
+        <v>0.30383240966666669</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>